--- a/analyst/Tracy/rmonize/data_dictionary/DD_CARLA_TRACY.xlsx
+++ b/analyst/Tracy/rmonize/data_dictionary/DD_CARLA_TRACY.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schwarz-f\Desktop\use-cases-harmonisation\analyst\Tracy\rmonize\data_dictionary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86FC02DA-F831-4A12-9453-961A546D13F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5663339B-C90E-4753-AB1F-14B6525604BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1249,7 +1249,7 @@
         <v>111</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>118</v>
+        <v>5</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
